--- a/testdata/import/05-universities.xlsx
+++ b/testdata/import/05-universities.xlsx
@@ -422,14 +422,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="31" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -440,20 +441,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>ИНН</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Сокращение</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Город</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ФИО Менеджера</t>
         </is>
@@ -465,22 +471,22 @@
           <t>Московский технический университет связи и информатики</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>МТУСИ</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>https://mtuci.ru</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Петров Пётр Алексеевич</t>
         </is>
@@ -492,22 +498,22 @@
           <t>Северо-Кавказский федеральный университет</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>СКФУ</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Ставрополь</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>https://www.ncfu.ru</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Егорова Дарья Константиновна</t>
         </is>
@@ -519,22 +525,22 @@
           <t>Томский государственный университет систем управления и радиоэлектроники</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>ТУСУР</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Томск</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>https://tusur.ru</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Попова Наталья Валерьевна</t>
         </is>
@@ -546,22 +552,22 @@
           <t>Северный (Арктический) федеральный университет имени М. В. Ломоносова</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>САФУ</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Архангельск</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>https://narfu.ru</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Лебедев Игорь Николаевич</t>
         </is>
@@ -573,22 +579,22 @@
           <t>Мордовский государственный университет им. Н. П. Огарёва</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>МГУ им. Огарёва</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Саранск</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>https://mrsu.ru</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Николаев Роман Сергеевич</t>
         </is>
@@ -600,29 +606,29 @@
           <t>Белгородский государственный технологический университет им. В. Г. Шухова</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>БГТУ им. Шухова</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Белгород</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>https://www.bstu.ru</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>ПГУ</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Пенза</t>
         </is>
